--- a/模版/填空题卡导入模板.xlsx
+++ b/模版/填空题卡导入模板.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="导入数据" sheetId="1" r:id="Rce34afa57ab140f4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="字段说明" sheetId="2" r:id="R244df9a3512c4415"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="导入数据" sheetId="1" r:id="R3f9e9370f30b4a62"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="字段说明" sheetId="2" r:id="Re70b427ed0c14fbf"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -14,14 +14,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="9">
+  <x:fonts count="3">
     <x:font>
       <x:sz val="11"/>
-      <x:name val="Carlito"/>
-    </x:font>
-    <x:font>
-      <x:sz val="11"/>
-      <x:color rgb="FFFFFFFF"/>
       <x:name val="Carlito"/>
     </x:font>
     <x:font>
@@ -31,36 +26,9 @@
       <x:name val="Carlito"/>
     </x:font>
     <x:font>
-      <x:b/>
-      <x:sz val="11"/>
-      <x:color rgb="FFFFFFFF"/>
-      <x:name val="Microsoft YaHei"/>
-    </x:font>
-    <x:font>
-      <x:sz val="11"/>
-      <x:name val="Microsoft YaHei"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:sz val="16"/>
-      <x:color rgb="FFFFFFFF"/>
-      <x:name val="Carlito"/>
-    </x:font>
-    <x:font>
       <x:sz val="11"/>
       <x:color rgb="FF7C2D12"/>
       <x:name val="Carlito"/>
-    </x:font>
-    <x:font>
-      <x:b/>
-      <x:sz val="16"/>
-      <x:color rgb="FFFFFFFF"/>
-      <x:name val="Microsoft YaHei"/>
-    </x:font>
-    <x:font>
-      <x:sz val="11"/>
-      <x:color rgb="FF7C2D12"/>
-      <x:name val="Microsoft YaHei"/>
     </x:font>
   </x:fonts>
   <x:fills count="5">
@@ -86,8 +54,38 @@
       </x:patternFill>
     </x:fill>
   </x:fills>
-  <x:borders count="10">
+  <x:borders count="13">
     <x:border/>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFF4C7A1"/>
+      </x:left>
+      <x:top style="thin">
+        <x:color rgb="FFF4C7A1"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFF4C7A1"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:top style="thin">
+        <x:color rgb="FFF4C7A1"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFF4C7A1"/>
+      </x:bottom>
+    </x:border>
+    <x:border>
+      <x:right style="thin">
+        <x:color rgb="FFF4C7A1"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFF4C7A1"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFF4C7A1"/>
+      </x:bottom>
+    </x:border>
     <x:border>
       <x:left style="thin">
         <x:color rgb="FFF4C7A1"/>
@@ -158,91 +156,122 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="39">
+  <x:cellXfs count="52">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -294,9 +323,9 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface="Calibri"/>
-        <a:cs typeface="Calibri"/>
+        <a:latin typeface="Calibri Light"/>
+        <a:ea typeface="Calibri Light"/>
+        <a:cs typeface="Calibri Light"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -448,136 +477,259 @@
   <x:cols>
     <x:col min="1" max="1" width="14" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="28" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="26" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="15.109999656677246" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="24.559999465942383" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="18" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="18" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="25" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="25" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="26" customHeight="1">
-      <x:c r="A1" s="10" t="str">
+      <x:c r="A1" s="12" t="str">
         <x:v>card_type</x:v>
       </x:c>
-      <x:c r="B1" s="11" t="str">
+      <x:c r="B1" s="13" t="str">
         <x:v>front</x:v>
       </x:c>
-      <x:c r="C1" s="11" t="str">
-        <x:v>back</x:v>
-      </x:c>
-      <x:c r="D1" s="11" t="str">
+      <x:c r="C1" s="13" t="str">
+        <x:v>answer1</x:v>
+      </x:c>
+      <x:c r="D1" s="13" t="str">
+        <x:v>answer1_alt1</x:v>
+      </x:c>
+      <x:c r="E1" s="13" t="str">
+        <x:v>answer1_alt2</x:v>
+      </x:c>
+      <x:c r="F1" s="13" t="str">
+        <x:v>answer2</x:v>
+      </x:c>
+      <x:c r="G1" s="13" t="str">
+        <x:v>answer2_alt1</x:v>
+      </x:c>
+      <x:c r="H1" s="13" t="str">
+        <x:v>answer2_alt2</x:v>
+      </x:c>
+      <x:c r="I1" s="13" t="str">
+        <x:v>blank_orderless</x:v>
+      </x:c>
+      <x:c r="J1" s="13" t="str">
         <x:v>example</x:v>
       </x:c>
-      <x:c r="E1" s="12" t="str">
+      <x:c r="K1" s="14" t="str">
         <x:v>note</x:v>
       </x:c>
     </x:row>
-    <x:row r="2">
-      <x:c r="A2" s="18" t="str">
+    <x:row r="2" ht="42" customHeight="1">
+      <x:c r="A2" s="33" t="str">
         <x:v>blank</x:v>
       </x:c>
-      <x:c r="B2" s="19" t="str">
+      <x:c r="B2" s="34" t="str">
         <x:v>I eat [] every day.</x:v>
       </x:c>
-      <x:c r="C2" s="19" t="str">
+      <x:c r="C2" s="34" t="str">
         <x:v>apple</x:v>
       </x:c>
-      <x:c r="D2" s="19" t="str">
+      <x:c r="D2" s="34" t="str">
+        <x:v>an apple</x:v>
+      </x:c>
+      <x:c r="E2" s="34" t="str">
+        <x:v>apples</x:v>
+      </x:c>
+      <x:c r="F2" s="34" t="str"/>
+      <x:c r="G2" s="34" t="str"/>
+      <x:c r="H2" s="34" t="str"/>
+      <x:c r="I2" s="34" t="str">
+        <x:v>false</x:v>
+      </x:c>
+      <x:c r="J2" s="34" t="str">
         <x:v>填写空格中的单词。</x:v>
       </x:c>
-      <x:c r="E2" s="20" t="str"/>
-    </x:row>
-    <x:row r="3">
-      <x:c r="A3" s="18" t="str">
+      <x:c r="K2" s="35" t="str"/>
+    </x:row>
+    <x:row r="3" ht="42" customHeight="1">
+      <x:c r="A3" s="36" t="str">
         <x:v>blank</x:v>
       </x:c>
-      <x:c r="B3" s="19" t="str">
-        <x:v>中国的首都是 []。</x:v>
-      </x:c>
-      <x:c r="C3" s="19" t="str">
-        <x:v>北京</x:v>
-      </x:c>
-      <x:c r="D3" s="19" t="str"/>
-      <x:c r="E3" s="20" t="str">
-        <x:v>占位符请使用 []，不要使用下划线</x:v>
+      <x:c r="B3" s="37" t="str">
+        <x:v>[] and [] are colours.</x:v>
+      </x:c>
+      <x:c r="C3" s="37" t="str">
+        <x:v>red</x:v>
+      </x:c>
+      <x:c r="D3" s="37" t="str">
+        <x:v>red colour</x:v>
+      </x:c>
+      <x:c r="E3" s="37" t="str"/>
+      <x:c r="F3" s="37" t="str">
+        <x:v>blue</x:v>
+      </x:c>
+      <x:c r="G3" s="37" t="str">
+        <x:v>blue colour</x:v>
+      </x:c>
+      <x:c r="H3" s="37" t="str"/>
+      <x:c r="I3" s="37" t="str">
+        <x:v>true</x:v>
+      </x:c>
+      <x:c r="J3" s="37" t="str">
+        <x:v>两个颜色可交换位置。</x:v>
+      </x:c>
+      <x:c r="K3" s="38" t="str">
+        <x:v>乱序仍按答案组一一配对</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
-      <x:c r="A4" s="18" t="str"/>
-      <x:c r="B4" s="19" t="str"/>
-      <x:c r="C4" s="19" t="str"/>
-      <x:c r="D4" s="19" t="str"/>
-      <x:c r="E4" s="20" t="str"/>
+      <x:c r="A4" s="36" t="str"/>
+      <x:c r="B4" s="37" t="str"/>
+      <x:c r="C4" s="37" t="str"/>
+      <x:c r="D4" s="37" t="str"/>
+      <x:c r="E4" s="37" t="str"/>
+      <x:c r="F4" s="37" t="str"/>
+      <x:c r="G4" s="37" t="str"/>
+      <x:c r="H4" s="37" t="str"/>
+      <x:c r="I4" s="37" t="str"/>
+      <x:c r="J4" s="37" t="str"/>
+      <x:c r="K4" s="38" t="str"/>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="18" t="str"/>
-      <x:c r="B5" s="19" t="str"/>
-      <x:c r="C5" s="19" t="str"/>
-      <x:c r="D5" s="19" t="str"/>
-      <x:c r="E5" s="20" t="str"/>
+      <x:c r="A5" s="36" t="str"/>
+      <x:c r="B5" s="37" t="str"/>
+      <x:c r="C5" s="37" t="str"/>
+      <x:c r="D5" s="37" t="str"/>
+      <x:c r="E5" s="37" t="str"/>
+      <x:c r="F5" s="37" t="str"/>
+      <x:c r="G5" s="37" t="str"/>
+      <x:c r="H5" s="37" t="str"/>
+      <x:c r="I5" s="37" t="str"/>
+      <x:c r="J5" s="37" t="str"/>
+      <x:c r="K5" s="38" t="str"/>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="18" t="str"/>
-      <x:c r="B6" s="19" t="str"/>
-      <x:c r="C6" s="19" t="str"/>
-      <x:c r="D6" s="19" t="str"/>
-      <x:c r="E6" s="20" t="str"/>
+      <x:c r="A6" s="36" t="str"/>
+      <x:c r="B6" s="37" t="str"/>
+      <x:c r="C6" s="37" t="str"/>
+      <x:c r="D6" s="37" t="str"/>
+      <x:c r="E6" s="37" t="str"/>
+      <x:c r="F6" s="37" t="str"/>
+      <x:c r="G6" s="37" t="str"/>
+      <x:c r="H6" s="37" t="str"/>
+      <x:c r="I6" s="37" t="str"/>
+      <x:c r="J6" s="37" t="str"/>
+      <x:c r="K6" s="38" t="str"/>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="18" t="str"/>
-      <x:c r="B7" s="19" t="str"/>
-      <x:c r="C7" s="19" t="str"/>
-      <x:c r="D7" s="19" t="str"/>
-      <x:c r="E7" s="20" t="str"/>
+      <x:c r="A7" s="36" t="str"/>
+      <x:c r="B7" s="37" t="str"/>
+      <x:c r="C7" s="37" t="str"/>
+      <x:c r="D7" s="37" t="str"/>
+      <x:c r="E7" s="37" t="str"/>
+      <x:c r="F7" s="37" t="str"/>
+      <x:c r="G7" s="37" t="str"/>
+      <x:c r="H7" s="37" t="str"/>
+      <x:c r="I7" s="37" t="str"/>
+      <x:c r="J7" s="37" t="str"/>
+      <x:c r="K7" s="38" t="str"/>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="18" t="str"/>
-      <x:c r="B8" s="19" t="str"/>
-      <x:c r="C8" s="19" t="str"/>
-      <x:c r="D8" s="19" t="str"/>
-      <x:c r="E8" s="20" t="str"/>
+      <x:c r="A8" s="36" t="str"/>
+      <x:c r="B8" s="37" t="str"/>
+      <x:c r="C8" s="37" t="str"/>
+      <x:c r="D8" s="37" t="str"/>
+      <x:c r="E8" s="37" t="str"/>
+      <x:c r="F8" s="37" t="str"/>
+      <x:c r="G8" s="37" t="str"/>
+      <x:c r="H8" s="37" t="str"/>
+      <x:c r="I8" s="37" t="str"/>
+      <x:c r="J8" s="37" t="str"/>
+      <x:c r="K8" s="38" t="str"/>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="18" t="str"/>
-      <x:c r="B9" s="19" t="str"/>
-      <x:c r="C9" s="19" t="str"/>
-      <x:c r="D9" s="19" t="str"/>
-      <x:c r="E9" s="20" t="str"/>
+      <x:c r="A9" s="36" t="str"/>
+      <x:c r="B9" s="37" t="str"/>
+      <x:c r="C9" s="37" t="str"/>
+      <x:c r="D9" s="37" t="str"/>
+      <x:c r="E9" s="37" t="str"/>
+      <x:c r="F9" s="37" t="str"/>
+      <x:c r="G9" s="37" t="str"/>
+      <x:c r="H9" s="37" t="str"/>
+      <x:c r="I9" s="37" t="str"/>
+      <x:c r="J9" s="37" t="str"/>
+      <x:c r="K9" s="38" t="str"/>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="18" t="str"/>
-      <x:c r="B10" s="19" t="str"/>
-      <x:c r="C10" s="19" t="str"/>
-      <x:c r="D10" s="19" t="str"/>
-      <x:c r="E10" s="20" t="str"/>
+      <x:c r="A10" s="36" t="str"/>
+      <x:c r="B10" s="37" t="str"/>
+      <x:c r="C10" s="37" t="str"/>
+      <x:c r="D10" s="37" t="str"/>
+      <x:c r="E10" s="37" t="str"/>
+      <x:c r="F10" s="37" t="str"/>
+      <x:c r="G10" s="37" t="str"/>
+      <x:c r="H10" s="37" t="str"/>
+      <x:c r="I10" s="37" t="str"/>
+      <x:c r="J10" s="37" t="str"/>
+      <x:c r="K10" s="38" t="str"/>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="18" t="str"/>
-      <x:c r="B11" s="19" t="str"/>
-      <x:c r="C11" s="19" t="str"/>
-      <x:c r="D11" s="19" t="str"/>
-      <x:c r="E11" s="20" t="str"/>
+      <x:c r="A11" s="36" t="str"/>
+      <x:c r="B11" s="37" t="str"/>
+      <x:c r="C11" s="37" t="str"/>
+      <x:c r="D11" s="37" t="str"/>
+      <x:c r="E11" s="37" t="str"/>
+      <x:c r="F11" s="37" t="str"/>
+      <x:c r="G11" s="37" t="str"/>
+      <x:c r="H11" s="37" t="str"/>
+      <x:c r="I11" s="37" t="str"/>
+      <x:c r="J11" s="37" t="str"/>
+      <x:c r="K11" s="38" t="str"/>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="18" t="str"/>
-      <x:c r="B12" s="19" t="str"/>
-      <x:c r="C12" s="19" t="str"/>
-      <x:c r="D12" s="19" t="str"/>
-      <x:c r="E12" s="20" t="str"/>
+      <x:c r="A12" s="36" t="str"/>
+      <x:c r="B12" s="37" t="str"/>
+      <x:c r="C12" s="37" t="str"/>
+      <x:c r="D12" s="37" t="str"/>
+      <x:c r="E12" s="37" t="str"/>
+      <x:c r="F12" s="37" t="str"/>
+      <x:c r="G12" s="37" t="str"/>
+      <x:c r="H12" s="37" t="str"/>
+      <x:c r="I12" s="37" t="str"/>
+      <x:c r="J12" s="37" t="str"/>
+      <x:c r="K12" s="38" t="str"/>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" s="18" t="str"/>
-      <x:c r="B13" s="19" t="str"/>
-      <x:c r="C13" s="19" t="str"/>
-      <x:c r="D13" s="19" t="str"/>
-      <x:c r="E13" s="20" t="str"/>
+      <x:c r="A13" s="36" t="str"/>
+      <x:c r="B13" s="37" t="str"/>
+      <x:c r="C13" s="37" t="str"/>
+      <x:c r="D13" s="37" t="str"/>
+      <x:c r="E13" s="37" t="str"/>
+      <x:c r="F13" s="37" t="str"/>
+      <x:c r="G13" s="37" t="str"/>
+      <x:c r="H13" s="37" t="str"/>
+      <x:c r="I13" s="37" t="str"/>
+      <x:c r="J13" s="37" t="str"/>
+      <x:c r="K13" s="38" t="str"/>
     </x:row>
     <x:row r="14">
-      <x:c r="A14" s="21" t="str"/>
-      <x:c r="B14" s="22" t="str"/>
-      <x:c r="C14" s="22" t="str"/>
-      <x:c r="D14" s="22" t="str"/>
-      <x:c r="E14" s="23" t="str"/>
+      <x:c r="A14" s="39" t="str"/>
+      <x:c r="B14" s="40" t="str"/>
+      <x:c r="C14" s="40" t="str"/>
+      <x:c r="D14" s="40" t="str"/>
+      <x:c r="E14" s="40" t="str"/>
+      <x:c r="F14" s="40" t="str"/>
+      <x:c r="G14" s="40" t="str"/>
+      <x:c r="H14" s="40" t="str"/>
+      <x:c r="I14" s="40" t="str"/>
+      <x:c r="J14" s="40" t="str"/>
+      <x:c r="K14" s="41" t="str"/>
     </x:row>
   </x:sheetData>
+  <x:dataValidations count="1">
+    <x:dataValidation type="list" sqref="I2:I100">
+      <x:formula1>"true,false"</x:formula1>
+    </x:dataValidation>
+  </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
@@ -586,109 +738,97 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="20" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="60" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="78" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1">
-      <x:c r="A1" s="35" t="str">
+    <x:row r="1" ht="30" customHeight="1">
+      <x:c r="A1" s="42" t="str">
         <x:v>填空题卡导入模板</x:v>
       </x:c>
-      <x:c r="B1" s="9"/>
-      <x:c r="C1" s="9"/>
-      <x:c r="D1" s="9"/>
-    </x:row>
-    <x:row r="2">
-      <x:c r="A2" s="9"/>
-      <x:c r="B2" s="9"/>
-      <x:c r="C2" s="9"/>
-      <x:c r="D2" s="9"/>
-    </x:row>
-    <x:row r="3">
-      <x:c r="A3" s="36" t="str">
-        <x:v>导入时保留第 1 行表头；front 中用 [] 表示空位，back 填正确答案。card_type 固定为 blank。</x:v>
-      </x:c>
-      <x:c r="B3" s="9"/>
-      <x:c r="C3" s="9"/>
-      <x:c r="D3" s="9"/>
-    </x:row>
-    <x:row r="4">
-      <x:c r="A4" s="9"/>
-      <x:c r="B4" s="9"/>
-      <x:c r="C4" s="9"/>
-      <x:c r="D4" s="9"/>
+      <x:c r="B1" s="42"/>
+      <x:c r="C1" s="42"/>
+      <x:c r="D1" s="42"/>
+    </x:row>
+    <x:row r="3" ht="44" customHeight="1">
+      <x:c r="A3" s="45" t="str">
+        <x:v>保留第 1 行表头；front 中每个 [] 对应一组 answerN，备选答案用 answerN_altM，乱序用 blank_orderless。card_type 固定为 blank。</x:v>
+      </x:c>
+      <x:c r="B3" s="45"/>
+      <x:c r="C3" s="45"/>
+      <x:c r="D3" s="45"/>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="37" t="str">
+      <x:c r="A5" s="47" t="str">
         <x:v>字段</x:v>
       </x:c>
-      <x:c r="B5" s="37" t="str">
+      <x:c r="B5" s="47" t="str">
         <x:v>说明</x:v>
       </x:c>
-      <x:c r="C5" s="9"/>
-      <x:c r="D5" s="9"/>
-    </x:row>
-    <x:row r="6">
-      <x:c r="A6" s="38" t="str">
+    </x:row>
+    <x:row r="6" ht="36" customHeight="1">
+      <x:c r="A6" s="51" t="str">
         <x:v>card_type</x:v>
       </x:c>
-      <x:c r="B6" s="38" t="str">
+      <x:c r="B6" s="51" t="str">
         <x:v>卡片类型，填空题卡固定填写 blank</x:v>
       </x:c>
-      <x:c r="C6" s="9"/>
-      <x:c r="D6" s="9"/>
-    </x:row>
-    <x:row r="7">
-      <x:c r="A7" s="38" t="str">
+    </x:row>
+    <x:row r="7" ht="36" customHeight="1">
+      <x:c r="A7" s="51" t="str">
         <x:v>front</x:v>
       </x:c>
-      <x:c r="B7" s="38" t="str">
-        <x:v>题干，必填；空位用 [] 表示</x:v>
-      </x:c>
-      <x:c r="C7" s="9"/>
-      <x:c r="D7" s="9"/>
-    </x:row>
-    <x:row r="8">
-      <x:c r="A8" s="38" t="str">
-        <x:v>back</x:v>
-      </x:c>
-      <x:c r="B8" s="38" t="str">
-        <x:v>正确答案，必填</x:v>
-      </x:c>
-      <x:c r="C8" s="9"/>
-      <x:c r="D8" s="9"/>
-    </x:row>
-    <x:row r="9">
-      <x:c r="A9" s="38" t="str">
+      <x:c r="B7" s="51" t="str">
+        <x:v>题干，必填；每个空位用 [] 表示</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="36" customHeight="1">
+      <x:c r="A8" s="51" t="str">
+        <x:v>answerN</x:v>
+      </x:c>
+      <x:c r="B8" s="51" t="str">
+        <x:v>第 N 个空的主答案，必填；编号必须从 1 连续到题干空位数</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="36" customHeight="1">
+      <x:c r="A9" s="51" t="str">
+        <x:v>answerN_altM</x:v>
+      </x:c>
+      <x:c r="B9" s="51" t="str">
+        <x:v>第 N 个空的第 M 个备选答案，可选；可按 answer3、answer3_alt1 等规律继续扩展</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="36" customHeight="1">
+      <x:c r="A10" s="51" t="str">
+        <x:v>blank_orderless</x:v>
+      </x:c>
+      <x:c r="B10" s="51" t="str">
+        <x:v>是否乱序填空；可填 true/false、yes/no、1/0 或 是/否，多空时才生效</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="36" customHeight="1">
+      <x:c r="A11" s="51" t="str">
+        <x:v>back（兼容）</x:v>
+      </x:c>
+      <x:c r="B11" s="51" t="str">
+        <x:v>旧模板仍可用 back 填答案；使用 answerN 新格式时不需要 back 列</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="36" customHeight="1">
+      <x:c r="A12" s="51" t="str">
         <x:v>example</x:v>
       </x:c>
-      <x:c r="B9" s="38" t="str">
+      <x:c r="B12" s="51" t="str">
         <x:v>解析或提示，可选</x:v>
       </x:c>
-      <x:c r="C9" s="9"/>
-      <x:c r="D9" s="9"/>
-    </x:row>
-    <x:row r="10">
-      <x:c r="A10" s="38" t="str">
+    </x:row>
+    <x:row r="13" ht="36" customHeight="1">
+      <x:c r="A13" s="51" t="str">
         <x:v>note</x:v>
       </x:c>
-      <x:c r="B10" s="38" t="str">
+      <x:c r="B13" s="51" t="str">
         <x:v>备注，可选</x:v>
       </x:c>
-      <x:c r="C10" s="9"/>
-      <x:c r="D10" s="9"/>
-    </x:row>
-    <x:row r="11">
-      <x:c r="A11" s="9"/>
-      <x:c r="B11" s="9"/>
-      <x:c r="C11" s="9"/>
-      <x:c r="D11" s="9"/>
-    </x:row>
-    <x:row r="12">
-      <x:c r="A12" s="9"/>
-      <x:c r="B12" s="9"/>
-      <x:c r="C12" s="9"/>
-      <x:c r="D12" s="9"/>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
